--- a/Configuration Generator/Config Drawings.xlsx
+++ b/Configuration Generator/Config Drawings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/13561f3231cadc0a/DTU/Comp_Arch_2/eFPGA/Configuration Generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="892" documentId="13_ncr:1_{FB05B031-63D2-4F22-8938-A1D344FEFB29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53C19ACF-1CE7-417D-A5D0-F30913020240}"/>
+  <xr:revisionPtr revIDLastSave="902" documentId="13_ncr:1_{FB05B031-63D2-4F22-8938-A1D344FEFB29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02E8583F-1E2C-4968-9F31-C611D0EB7735}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Logic_Slice" sheetId="4" r:id="rId1"/>
@@ -335,7 +335,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -360,9 +360,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -378,6 +379,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -683,49 +688,49 @@
       <c r="L1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="N1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="O1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="P1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="R1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="S1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="T1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="U1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="V1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="W1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="X1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA1" s="23" t="s">
+      <c r="M1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" t="s">
+        <v>4</v>
+      </c>
+      <c r="O1" t="s">
+        <v>4</v>
+      </c>
+      <c r="P1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>4</v>
+      </c>
+      <c r="R1" t="s">
+        <v>4</v>
+      </c>
+      <c r="S1" t="s">
+        <v>4</v>
+      </c>
+      <c r="T1" t="s">
+        <v>4</v>
+      </c>
+      <c r="U1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V1" t="s">
+        <v>4</v>
+      </c>
+      <c r="W1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA1" t="s">
         <v>4</v>
       </c>
       <c r="AB1" t="s">
@@ -749,49 +754,49 @@
       <c r="AH1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="AI1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AS1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AV1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AW1" s="23" t="s">
+      <c r="AI1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW1" t="s">
         <v>4</v>
       </c>
       <c r="AX1" t="s">
@@ -815,46 +820,46 @@
       <c r="BD1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="BE1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BF1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BG1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BH1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BI1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BJ1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BK1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BL1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BM1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BN1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BO1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BP1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BQ1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BR1" s="23" t="s">
+      <c r="BE1" t="s">
+        <v>4</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>4</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>4</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>4</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>4</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>4</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>4</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>4</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>4</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>4</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>4</v>
+      </c>
+      <c r="BR1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -895,49 +900,49 @@
       <c r="L2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="M2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="N2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="O2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="P2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="R2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="S2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="T2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="U2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="V2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="W2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="X2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA2" s="23" t="s">
+      <c r="M2" t="s">
+        <v>4</v>
+      </c>
+      <c r="N2" t="s">
+        <v>4</v>
+      </c>
+      <c r="O2" t="s">
+        <v>4</v>
+      </c>
+      <c r="P2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R2" t="s">
+        <v>4</v>
+      </c>
+      <c r="S2" t="s">
+        <v>4</v>
+      </c>
+      <c r="T2" t="s">
+        <v>4</v>
+      </c>
+      <c r="U2" t="s">
+        <v>4</v>
+      </c>
+      <c r="V2" t="s">
+        <v>4</v>
+      </c>
+      <c r="W2" t="s">
+        <v>4</v>
+      </c>
+      <c r="X2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA2" t="s">
         <v>4</v>
       </c>
       <c r="AB2" t="s">
@@ -961,49 +966,49 @@
       <c r="AH2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="AI2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AS2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AV2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AW2" s="23" t="s">
+      <c r="AI2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW2" t="s">
         <v>4</v>
       </c>
       <c r="AX2" t="s">
@@ -1027,46 +1032,46 @@
       <c r="BD2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="BE2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BF2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BG2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BH2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BI2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BJ2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BK2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BL2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BM2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BN2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BO2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BP2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BQ2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BR2" s="23" t="s">
+      <c r="BE2" t="s">
+        <v>4</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>4</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>4</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>4</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>4</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>4</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>4</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>4</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>4</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>4</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>4</v>
+      </c>
+      <c r="BR2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1107,49 +1112,49 @@
       <c r="L3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="N3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="O3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="P3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="R3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="S3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="T3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="U3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="V3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="W3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="X3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA3" s="23" t="s">
+      <c r="M3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA3" t="s">
         <v>4</v>
       </c>
       <c r="AB3" t="s">
@@ -1173,49 +1178,49 @@
       <c r="AH3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="AI3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AS3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AV3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AW3" s="23" t="s">
+      <c r="AI3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW3" t="s">
         <v>4</v>
       </c>
       <c r="AX3" t="s">
@@ -1239,46 +1244,46 @@
       <c r="BD3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="BE3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BF3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BG3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BH3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BI3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BJ3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BK3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BL3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BM3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BN3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BO3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BP3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BQ3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BR3" s="23" t="s">
+      <c r="BE3" t="s">
+        <v>4</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>4</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>4</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>4</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>4</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>4</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>4</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>4</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>4</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>4</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>4</v>
+      </c>
+      <c r="BR3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2567,10 +2572,10 @@
       <c r="D10" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E10" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="23" t="s">
+      <c r="E10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" t="s">
         <v>4</v>
       </c>
       <c r="G10" s="1" t="s">
@@ -2633,10 +2638,10 @@
       <c r="Z10" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="AA10" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB10" s="23" t="s">
+      <c r="AA10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB10" t="s">
         <v>4</v>
       </c>
       <c r="AC10" s="1" t="s">
@@ -2699,10 +2704,10 @@
       <c r="AV10" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="AW10" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AX10" s="23" t="s">
+      <c r="AW10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AX10" t="s">
         <v>4</v>
       </c>
       <c r="AY10" s="1" t="s">
@@ -2779,10 +2784,10 @@
       <c r="D11" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F11" s="23" t="s">
+      <c r="E11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" t="s">
         <v>4</v>
       </c>
       <c r="G11" s="17" t="s">
@@ -2845,10 +2850,10 @@
       <c r="Z11" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="AA11" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB11" s="23" t="s">
+      <c r="AA11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB11" t="s">
         <v>4</v>
       </c>
       <c r="AC11" s="17" t="s">
@@ -2911,10 +2916,10 @@
       <c r="AV11" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="AW11" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AX11" s="23" t="s">
+      <c r="AW11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AX11" t="s">
         <v>4</v>
       </c>
       <c r="AY11" s="17" t="s">
@@ -2979,22 +2984,22 @@
       </c>
     </row>
     <row r="12" spans="1:70" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="21" t="s">
+      <c r="A12" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="B12" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="23" t="s">
+      <c r="C12" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="4" t="s">
@@ -3045,22 +3050,22 @@
       <c r="V12" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="W12" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="X12" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y12" s="21" t="s">
+      <c r="W12" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="Z12" s="22" t="s">
+      <c r="X12" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="AA12" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB12" s="23" t="s">
+      <c r="Y12" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z12" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA12" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB12" t="s">
         <v>4</v>
       </c>
       <c r="AC12" s="4" t="s">
@@ -3111,22 +3116,22 @@
       <c r="AR12" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="AS12" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT12" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU12" s="21" t="s">
+      <c r="AS12" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="AV12" s="22" t="s">
+      <c r="AT12" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="AW12" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AX12" s="23" t="s">
+      <c r="AU12" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV12" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW12" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AX12" t="s">
         <v>4</v>
       </c>
       <c r="AY12" s="4" t="s">
@@ -3177,17 +3182,17 @@
       <c r="BN12" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="BO12" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="BP12" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="BQ12" s="21" t="s">
+      <c r="BO12" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="BR12" s="22" t="s">
+      <c r="BP12" s="22" t="s">
         <v>3</v>
+      </c>
+      <c r="BQ12" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="BR12" s="24" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:70" x14ac:dyDescent="0.35">
@@ -4475,10 +4480,10 @@
       <c r="D19" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E19" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F19" s="23" t="s">
+      <c r="E19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" t="s">
         <v>4</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -4541,10 +4546,10 @@
       <c r="Z19" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="AA19" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB19" s="23" t="s">
+      <c r="AA19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB19" t="s">
         <v>4</v>
       </c>
       <c r="AC19" s="1" t="s">
@@ -4607,10 +4612,10 @@
       <c r="AV19" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="AW19" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AX19" s="23" t="s">
+      <c r="AW19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AX19" t="s">
         <v>4</v>
       </c>
       <c r="AY19" s="1" t="s">
@@ -4687,10 +4692,10 @@
       <c r="D20" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E20" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="23" t="s">
+      <c r="E20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" t="s">
         <v>4</v>
       </c>
       <c r="G20" s="17" t="s">
@@ -4753,10 +4758,10 @@
       <c r="Z20" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="AA20" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB20" s="23" t="s">
+      <c r="AA20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB20" t="s">
         <v>4</v>
       </c>
       <c r="AC20" s="17" t="s">
@@ -4819,10 +4824,10 @@
       <c r="AV20" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="AW20" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AX20" s="23" t="s">
+      <c r="AW20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AX20" t="s">
         <v>4</v>
       </c>
       <c r="AY20" s="17" t="s">
@@ -4887,22 +4892,22 @@
       </c>
     </row>
     <row r="21" spans="1:70" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="21" t="s">
+      <c r="A21" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="B21" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E21" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="23" t="s">
+      <c r="C21" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" t="s">
         <v>4</v>
       </c>
       <c r="G21" s="4" t="s">
@@ -4953,22 +4958,22 @@
       <c r="V21" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="W21" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="X21" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y21" s="21" t="s">
+      <c r="W21" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="Z21" s="22" t="s">
+      <c r="X21" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="AA21" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB21" s="23" t="s">
+      <c r="Y21" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z21" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB21" t="s">
         <v>4</v>
       </c>
       <c r="AC21" s="4" t="s">
@@ -5019,22 +5024,22 @@
       <c r="AR21" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="AS21" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT21" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU21" s="21" t="s">
+      <c r="AS21" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="AV21" s="22" t="s">
+      <c r="AT21" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="AW21" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AX21" s="23" t="s">
+      <c r="AU21" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV21" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AX21" t="s">
         <v>4</v>
       </c>
       <c r="AY21" s="4" t="s">
@@ -5085,17 +5090,17 @@
       <c r="BN21" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="BO21" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="BP21" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="BQ21" s="21" t="s">
+      <c r="BO21" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="BR21" s="22" t="s">
+      <c r="BP21" s="22" t="s">
         <v>3</v>
+      </c>
+      <c r="BQ21" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="BR21" s="24" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:70" x14ac:dyDescent="0.35">
@@ -6383,10 +6388,10 @@
       <c r="D28" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E28" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F28" s="23" t="s">
+      <c r="E28" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28" t="s">
         <v>4</v>
       </c>
       <c r="G28" s="1" t="s">
@@ -6449,10 +6454,10 @@
       <c r="Z28" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="AA28" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB28" s="23" t="s">
+      <c r="AA28" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB28" t="s">
         <v>4</v>
       </c>
       <c r="AC28" s="1" t="s">
@@ -6515,10 +6520,10 @@
       <c r="AV28" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="AW28" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AX28" s="23" t="s">
+      <c r="AW28" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AX28" t="s">
         <v>4</v>
       </c>
       <c r="AY28" s="1" t="s">
@@ -6595,10 +6600,10 @@
       <c r="D29" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E29" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29" s="23" t="s">
+      <c r="E29" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29" t="s">
         <v>4</v>
       </c>
       <c r="G29" s="17" t="s">
@@ -6661,10 +6666,10 @@
       <c r="Z29" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="AA29" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB29" s="23" t="s">
+      <c r="AA29" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB29" t="s">
         <v>4</v>
       </c>
       <c r="AC29" s="17" t="s">
@@ -6727,10 +6732,10 @@
       <c r="AV29" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="AW29" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AX29" s="23" t="s">
+      <c r="AW29" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AX29" t="s">
         <v>4</v>
       </c>
       <c r="AY29" s="17" t="s">
@@ -6795,22 +6800,22 @@
       </c>
     </row>
     <row r="30" spans="1:70" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C30" s="21" t="s">
+      <c r="A30" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="B30" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F30" s="23" t="s">
+      <c r="C30" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30" t="s">
         <v>4</v>
       </c>
       <c r="G30" s="4" t="s">
@@ -6861,22 +6866,22 @@
       <c r="V30" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="W30" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="X30" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y30" s="21" t="s">
+      <c r="W30" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="Z30" s="22" t="s">
+      <c r="X30" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="AA30" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB30" s="23" t="s">
+      <c r="Y30" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z30" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA30" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB30" t="s">
         <v>4</v>
       </c>
       <c r="AC30" s="4" t="s">
@@ -6927,22 +6932,22 @@
       <c r="AR30" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="AS30" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT30" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU30" s="21" t="s">
+      <c r="AS30" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="AV30" s="22" t="s">
+      <c r="AT30" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="AW30" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AX30" s="23" t="s">
+      <c r="AU30" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV30" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW30" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AX30" t="s">
         <v>4</v>
       </c>
       <c r="AY30" s="4" t="s">
@@ -6993,17 +6998,17 @@
       <c r="BN30" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="BO30" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="BP30" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="BQ30" s="21" t="s">
+      <c r="BO30" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="BR30" s="22" t="s">
+      <c r="BP30" s="22" t="s">
         <v>3</v>
+      </c>
+      <c r="BQ30" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="BR30" s="24" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:70" x14ac:dyDescent="0.35">
@@ -8291,28 +8296,28 @@
       <c r="D37" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E37" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F37" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G37" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="H37" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I37" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J37" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="K37" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="L37" s="25" t="s">
+      <c r="E37" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" t="s">
+        <v>4</v>
+      </c>
+      <c r="G37" t="s">
+        <v>4</v>
+      </c>
+      <c r="H37" t="s">
+        <v>4</v>
+      </c>
+      <c r="I37" t="s">
+        <v>4</v>
+      </c>
+      <c r="J37" t="s">
+        <v>4</v>
+      </c>
+      <c r="K37" t="s">
+        <v>4</v>
+      </c>
+      <c r="L37" s="5" t="s">
         <v>4</v>
       </c>
       <c r="M37" s="4" t="s">
@@ -8357,28 +8362,28 @@
       <c r="Z37" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="AA37" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB37" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC37" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD37" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE37" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF37" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG37" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH37" s="25" t="s">
+      <c r="AA37" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE37" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF37" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG37" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH37" s="5" t="s">
         <v>4</v>
       </c>
       <c r="AI37" s="4" t="s">
@@ -8423,28 +8428,28 @@
       <c r="AV37" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="AW37" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AX37" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AY37" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AZ37" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BA37" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BB37" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BC37" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BD37" s="25" t="s">
+      <c r="AW37" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AX37" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY37" t="s">
+        <v>4</v>
+      </c>
+      <c r="AZ37" t="s">
+        <v>4</v>
+      </c>
+      <c r="BA37" t="s">
+        <v>4</v>
+      </c>
+      <c r="BB37" t="s">
+        <v>4</v>
+      </c>
+      <c r="BC37" t="s">
+        <v>4</v>
+      </c>
+      <c r="BD37" s="5" t="s">
         <v>4</v>
       </c>
       <c r="BE37" s="4" t="s">
@@ -8490,38 +8495,38 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:70" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:70" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B38" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C38" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="E38" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F38" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G38" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="H38" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I38" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J38" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="K38" s="23" t="s">
+      <c r="C38" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F38" t="s">
+        <v>4</v>
+      </c>
+      <c r="G38" t="s">
+        <v>4</v>
+      </c>
+      <c r="H38" t="s">
+        <v>4</v>
+      </c>
+      <c r="I38" t="s">
+        <v>4</v>
+      </c>
+      <c r="J38" t="s">
+        <v>4</v>
+      </c>
+      <c r="K38" t="s">
         <v>4</v>
       </c>
       <c r="L38" t="s">
@@ -8563,31 +8568,31 @@
       <c r="X38" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="Y38" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z38" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA38" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB38" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC38" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD38" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE38" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF38" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG38" s="23" t="s">
+      <c r="Y38" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z38" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA38" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE38" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF38" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG38" t="s">
         <v>4</v>
       </c>
       <c r="AH38" t="s">
@@ -8629,31 +8634,31 @@
       <c r="AT38" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="AU38" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="AV38" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="AW38" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AX38" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AY38" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AZ38" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BA38" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BB38" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BC38" s="23" t="s">
+      <c r="AU38" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="AV38" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="AW38" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AX38" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY38" t="s">
+        <v>4</v>
+      </c>
+      <c r="AZ38" t="s">
+        <v>4</v>
+      </c>
+      <c r="BA38" t="s">
+        <v>4</v>
+      </c>
+      <c r="BB38" t="s">
+        <v>4</v>
+      </c>
+      <c r="BC38" t="s">
         <v>4</v>
       </c>
       <c r="BD38" t="s">
@@ -8695,45 +8700,45 @@
       <c r="BP38" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="BQ38" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="BR38" s="18" t="s">
+      <c r="BQ38" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="BR38" s="5" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:70" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C39" s="21" t="s">
+      <c r="A39" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="D39" s="22" t="s">
+      <c r="B39" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E39" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F39" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G39" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="H39" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I39" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J39" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="K39" s="23" t="s">
+      <c r="C39" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F39" t="s">
+        <v>4</v>
+      </c>
+      <c r="G39" t="s">
+        <v>4</v>
+      </c>
+      <c r="H39" t="s">
+        <v>4</v>
+      </c>
+      <c r="I39" t="s">
+        <v>4</v>
+      </c>
+      <c r="J39" t="s">
+        <v>4</v>
+      </c>
+      <c r="K39" t="s">
         <v>4</v>
       </c>
       <c r="L39" t="s">
@@ -8769,37 +8774,37 @@
       <c r="V39" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="W39" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="X39" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y39" s="21" t="s">
+      <c r="W39" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="Z39" s="22" t="s">
+      <c r="X39" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="AA39" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB39" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC39" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD39" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE39" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF39" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG39" s="23" t="s">
+      <c r="Y39" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z39" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA39" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE39" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF39" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG39" t="s">
         <v>4</v>
       </c>
       <c r="AH39" t="s">
@@ -8835,37 +8840,37 @@
       <c r="AR39" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="AS39" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT39" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU39" s="21" t="s">
+      <c r="AS39" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="AV39" s="22" t="s">
+      <c r="AT39" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="AW39" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="AX39" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AY39" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AZ39" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BA39" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BB39" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BC39" s="23" t="s">
+      <c r="AU39" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV39" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW39" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AX39" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY39" t="s">
+        <v>4</v>
+      </c>
+      <c r="AZ39" t="s">
+        <v>4</v>
+      </c>
+      <c r="BA39" t="s">
+        <v>4</v>
+      </c>
+      <c r="BB39" t="s">
+        <v>4</v>
+      </c>
+      <c r="BC39" t="s">
         <v>4</v>
       </c>
       <c r="BD39" t="s">
@@ -8901,228 +8906,228 @@
       <c r="BN39" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="BO39" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="BP39" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="BQ39" s="21" t="s">
+      <c r="BO39" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="BR39" s="22" t="s">
+      <c r="BP39" s="22" t="s">
         <v>3</v>
+      </c>
+      <c r="BQ39" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="BR39" s="27" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:70" x14ac:dyDescent="0.35">
-      <c r="A40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="E40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="H40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="K40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="L40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="M40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="N40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="O40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="P40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="R40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="S40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="T40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="U40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="V40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="W40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="X40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AS40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AV40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AW40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AX40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AY40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AZ40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BA40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BB40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BC40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BD40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BE40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BF40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BG40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BH40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BI40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BJ40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BK40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BL40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BM40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BN40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BO40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BP40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BQ40" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="BR40" s="23" t="s">
+      <c r="A40" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" t="s">
+        <v>4</v>
+      </c>
+      <c r="E40" t="s">
+        <v>4</v>
+      </c>
+      <c r="F40" t="s">
+        <v>4</v>
+      </c>
+      <c r="G40" t="s">
+        <v>4</v>
+      </c>
+      <c r="H40" t="s">
+        <v>4</v>
+      </c>
+      <c r="I40" t="s">
+        <v>4</v>
+      </c>
+      <c r="J40" t="s">
+        <v>4</v>
+      </c>
+      <c r="K40" t="s">
+        <v>4</v>
+      </c>
+      <c r="L40" t="s">
+        <v>4</v>
+      </c>
+      <c r="M40" t="s">
+        <v>4</v>
+      </c>
+      <c r="N40" t="s">
+        <v>4</v>
+      </c>
+      <c r="O40" t="s">
+        <v>4</v>
+      </c>
+      <c r="P40" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>4</v>
+      </c>
+      <c r="R40" t="s">
+        <v>4</v>
+      </c>
+      <c r="S40" t="s">
+        <v>4</v>
+      </c>
+      <c r="T40" t="s">
+        <v>4</v>
+      </c>
+      <c r="U40" t="s">
+        <v>4</v>
+      </c>
+      <c r="V40" t="s">
+        <v>4</v>
+      </c>
+      <c r="W40" t="s">
+        <v>4</v>
+      </c>
+      <c r="X40" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AX40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY40" t="s">
+        <v>4</v>
+      </c>
+      <c r="AZ40" t="s">
+        <v>4</v>
+      </c>
+      <c r="BA40" t="s">
+        <v>4</v>
+      </c>
+      <c r="BB40" t="s">
+        <v>4</v>
+      </c>
+      <c r="BC40" t="s">
+        <v>4</v>
+      </c>
+      <c r="BD40" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE40" t="s">
+        <v>4</v>
+      </c>
+      <c r="BF40" t="s">
+        <v>4</v>
+      </c>
+      <c r="BG40" t="s">
+        <v>4</v>
+      </c>
+      <c r="BH40" t="s">
+        <v>4</v>
+      </c>
+      <c r="BI40" t="s">
+        <v>4</v>
+      </c>
+      <c r="BJ40" t="s">
+        <v>4</v>
+      </c>
+      <c r="BK40" t="s">
+        <v>4</v>
+      </c>
+      <c r="BL40" t="s">
+        <v>4</v>
+      </c>
+      <c r="BM40" t="s">
+        <v>4</v>
+      </c>
+      <c r="BN40" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO40" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP40" t="s">
+        <v>4</v>
+      </c>
+      <c r="BQ40" t="s">
+        <v>4</v>
+      </c>
+      <c r="BR40" t="s">
         <v>4</v>
       </c>
     </row>
@@ -21743,22 +21748,22 @@
       </c>
     </row>
     <row r="50" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="E50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F50" s="23" t="s">
+      <c r="A50" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" t="s">
+        <v>4</v>
+      </c>
+      <c r="E50" t="s">
+        <v>4</v>
+      </c>
+      <c r="F50" t="s">
         <v>4</v>
       </c>
       <c r="G50" s="1" t="s">
@@ -21791,22 +21796,22 @@
       <c r="P50" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="Q50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="R50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="S50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="T50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="U50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="V50" s="23" t="s">
+      <c r="Q50" t="s">
+        <v>4</v>
+      </c>
+      <c r="R50" t="s">
+        <v>4</v>
+      </c>
+      <c r="S50" t="s">
+        <v>4</v>
+      </c>
+      <c r="T50" t="s">
+        <v>4</v>
+      </c>
+      <c r="U50" t="s">
+        <v>4</v>
+      </c>
+      <c r="V50" t="s">
         <v>4</v>
       </c>
       <c r="W50" s="1" t="s">
@@ -21839,72 +21844,72 @@
       <c r="AF50" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="AG50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AS50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AV50" s="23" t="s">
+      <c r="AG50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV50" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="E51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F51" s="23" t="s">
+      <c r="A51" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" t="s">
+        <v>4</v>
+      </c>
+      <c r="E51" t="s">
+        <v>4</v>
+      </c>
+      <c r="F51" t="s">
         <v>4</v>
       </c>
       <c r="G51" s="4" t="s">
@@ -21937,22 +21942,22 @@
       <c r="P51" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="Q51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="R51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="S51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="T51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="U51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="V51" s="23" t="s">
+      <c r="Q51" t="s">
+        <v>4</v>
+      </c>
+      <c r="R51" t="s">
+        <v>4</v>
+      </c>
+      <c r="S51" t="s">
+        <v>4</v>
+      </c>
+      <c r="T51" t="s">
+        <v>4</v>
+      </c>
+      <c r="U51" t="s">
+        <v>4</v>
+      </c>
+      <c r="V51" t="s">
         <v>4</v>
       </c>
       <c r="W51" s="4" t="s">
@@ -21985,72 +21990,72 @@
       <c r="AF51" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="AG51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AS51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AV51" s="23" t="s">
+      <c r="AG51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV51" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="E52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F52" s="23" t="s">
+      <c r="A52" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" t="s">
         <v>4</v>
       </c>
       <c r="G52" s="4" t="s">
@@ -22083,22 +22088,22 @@
       <c r="P52" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="Q52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="R52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="S52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="T52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="U52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="V52" s="23" t="s">
+      <c r="Q52" t="s">
+        <v>4</v>
+      </c>
+      <c r="R52" t="s">
+        <v>4</v>
+      </c>
+      <c r="S52" t="s">
+        <v>4</v>
+      </c>
+      <c r="T52" t="s">
+        <v>4</v>
+      </c>
+      <c r="U52" t="s">
+        <v>4</v>
+      </c>
+      <c r="V52" t="s">
         <v>4</v>
       </c>
       <c r="W52" s="4" t="s">
@@ -22131,72 +22136,72 @@
       <c r="AF52" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="AG52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AS52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AV52" s="23" t="s">
+      <c r="AG52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV52" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="E53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F53" s="23" t="s">
+      <c r="A53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" t="s">
+        <v>4</v>
+      </c>
+      <c r="E53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F53" t="s">
         <v>4</v>
       </c>
       <c r="G53" s="4" t="s">
@@ -22229,22 +22234,22 @@
       <c r="P53" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="Q53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="R53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="S53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="T53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="U53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="V53" s="23" t="s">
+      <c r="Q53" t="s">
+        <v>4</v>
+      </c>
+      <c r="R53" t="s">
+        <v>4</v>
+      </c>
+      <c r="S53" t="s">
+        <v>4</v>
+      </c>
+      <c r="T53" t="s">
+        <v>4</v>
+      </c>
+      <c r="U53" t="s">
+        <v>4</v>
+      </c>
+      <c r="V53" t="s">
         <v>4</v>
       </c>
       <c r="W53" s="4" t="s">
@@ -22277,72 +22282,72 @@
       <c r="AF53" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="AG53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AS53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AV53" s="23" t="s">
+      <c r="AG53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV53" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="E54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F54" s="23" t="s">
+      <c r="A54" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" t="s">
+        <v>4</v>
+      </c>
+      <c r="D54" t="s">
+        <v>4</v>
+      </c>
+      <c r="E54" t="s">
+        <v>4</v>
+      </c>
+      <c r="F54" t="s">
         <v>4</v>
       </c>
       <c r="G54" s="4" t="s">
@@ -22375,22 +22380,22 @@
       <c r="P54" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="Q54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="R54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="S54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="T54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="U54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="V54" s="23" t="s">
+      <c r="Q54" t="s">
+        <v>4</v>
+      </c>
+      <c r="R54" t="s">
+        <v>4</v>
+      </c>
+      <c r="S54" t="s">
+        <v>4</v>
+      </c>
+      <c r="T54" t="s">
+        <v>4</v>
+      </c>
+      <c r="U54" t="s">
+        <v>4</v>
+      </c>
+      <c r="V54" t="s">
         <v>4</v>
       </c>
       <c r="W54" s="4" t="s">
@@ -22423,72 +22428,72 @@
       <c r="AF54" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="AG54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AS54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AV54" s="23" t="s">
+      <c r="AG54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV54" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="E55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F55" s="23" t="s">
+      <c r="A55" t="s">
+        <v>4</v>
+      </c>
+      <c r="B55" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" t="s">
+        <v>4</v>
+      </c>
+      <c r="E55" t="s">
+        <v>4</v>
+      </c>
+      <c r="F55" t="s">
         <v>4</v>
       </c>
       <c r="G55" s="6" t="s">
@@ -22521,22 +22526,22 @@
       <c r="P55" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="Q55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="R55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="S55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="T55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="U55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="V55" s="23" t="s">
+      <c r="Q55" t="s">
+        <v>4</v>
+      </c>
+      <c r="R55" t="s">
+        <v>4</v>
+      </c>
+      <c r="S55" t="s">
+        <v>4</v>
+      </c>
+      <c r="T55" t="s">
+        <v>4</v>
+      </c>
+      <c r="U55" t="s">
+        <v>4</v>
+      </c>
+      <c r="V55" t="s">
         <v>4</v>
       </c>
       <c r="W55" s="6" t="s">
@@ -22569,198 +22574,198 @@
       <c r="AF55" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="AG55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AS55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AV55" s="23" t="s">
+      <c r="AG55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV55" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="E56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="H56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="K56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="L56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="M56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="N56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="O56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="P56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="R56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="S56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="T56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="U56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="V56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="W56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="X56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AS56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AV56" s="23" t="s">
+      <c r="A56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56" t="s">
+        <v>4</v>
+      </c>
+      <c r="E56" t="s">
+        <v>4</v>
+      </c>
+      <c r="F56" t="s">
+        <v>4</v>
+      </c>
+      <c r="G56" t="s">
+        <v>4</v>
+      </c>
+      <c r="H56" t="s">
+        <v>4</v>
+      </c>
+      <c r="I56" t="s">
+        <v>4</v>
+      </c>
+      <c r="J56" t="s">
+        <v>4</v>
+      </c>
+      <c r="K56" t="s">
+        <v>4</v>
+      </c>
+      <c r="L56" t="s">
+        <v>4</v>
+      </c>
+      <c r="M56" t="s">
+        <v>4</v>
+      </c>
+      <c r="N56" t="s">
+        <v>4</v>
+      </c>
+      <c r="O56" t="s">
+        <v>4</v>
+      </c>
+      <c r="P56" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>4</v>
+      </c>
+      <c r="R56" t="s">
+        <v>4</v>
+      </c>
+      <c r="S56" t="s">
+        <v>4</v>
+      </c>
+      <c r="T56" t="s">
+        <v>4</v>
+      </c>
+      <c r="U56" t="s">
+        <v>4</v>
+      </c>
+      <c r="V56" t="s">
+        <v>4</v>
+      </c>
+      <c r="W56" t="s">
+        <v>4</v>
+      </c>
+      <c r="X56" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV56" t="s">
         <v>4</v>
       </c>
     </row>
@@ -27592,7 +27597,7 @@
       <c r="P33" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="Q33" s="26" t="s">
+      <c r="Q33" s="10" t="s">
         <v>4</v>
       </c>
       <c r="R33" s="12" t="s">
@@ -30077,1045 +30082,1045 @@
       </c>
     </row>
     <row r="50" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="E50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="H50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="K50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="L50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="M50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="N50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="O50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="P50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="R50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="S50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="T50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="U50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="V50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="W50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="X50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AS50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AV50" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AW50" s="23" t="s">
+      <c r="A50" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" t="s">
+        <v>4</v>
+      </c>
+      <c r="E50" t="s">
+        <v>4</v>
+      </c>
+      <c r="F50" t="s">
+        <v>4</v>
+      </c>
+      <c r="G50" t="s">
+        <v>4</v>
+      </c>
+      <c r="H50" t="s">
+        <v>4</v>
+      </c>
+      <c r="I50" t="s">
+        <v>4</v>
+      </c>
+      <c r="J50" t="s">
+        <v>4</v>
+      </c>
+      <c r="K50" t="s">
+        <v>4</v>
+      </c>
+      <c r="L50" t="s">
+        <v>4</v>
+      </c>
+      <c r="M50" t="s">
+        <v>4</v>
+      </c>
+      <c r="N50" t="s">
+        <v>4</v>
+      </c>
+      <c r="O50" t="s">
+        <v>4</v>
+      </c>
+      <c r="P50" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>4</v>
+      </c>
+      <c r="R50" t="s">
+        <v>4</v>
+      </c>
+      <c r="S50" t="s">
+        <v>4</v>
+      </c>
+      <c r="T50" t="s">
+        <v>4</v>
+      </c>
+      <c r="U50" t="s">
+        <v>4</v>
+      </c>
+      <c r="V50" t="s">
+        <v>4</v>
+      </c>
+      <c r="W50" t="s">
+        <v>4</v>
+      </c>
+      <c r="X50" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV50" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW50" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="E51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="H51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="K51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="L51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="M51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="N51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="O51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="P51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="R51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="S51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="T51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="U51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="V51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="W51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="X51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AS51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AV51" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AW51" s="23" t="s">
+      <c r="A51" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" t="s">
+        <v>4</v>
+      </c>
+      <c r="E51" t="s">
+        <v>4</v>
+      </c>
+      <c r="F51" t="s">
+        <v>4</v>
+      </c>
+      <c r="G51" t="s">
+        <v>4</v>
+      </c>
+      <c r="H51" t="s">
+        <v>4</v>
+      </c>
+      <c r="I51" t="s">
+        <v>4</v>
+      </c>
+      <c r="J51" t="s">
+        <v>4</v>
+      </c>
+      <c r="K51" t="s">
+        <v>4</v>
+      </c>
+      <c r="L51" t="s">
+        <v>4</v>
+      </c>
+      <c r="M51" t="s">
+        <v>4</v>
+      </c>
+      <c r="N51" t="s">
+        <v>4</v>
+      </c>
+      <c r="O51" t="s">
+        <v>4</v>
+      </c>
+      <c r="P51" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>4</v>
+      </c>
+      <c r="R51" t="s">
+        <v>4</v>
+      </c>
+      <c r="S51" t="s">
+        <v>4</v>
+      </c>
+      <c r="T51" t="s">
+        <v>4</v>
+      </c>
+      <c r="U51" t="s">
+        <v>4</v>
+      </c>
+      <c r="V51" t="s">
+        <v>4</v>
+      </c>
+      <c r="W51" t="s">
+        <v>4</v>
+      </c>
+      <c r="X51" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV51" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW51" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="E52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="H52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="K52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="L52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="M52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="N52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="O52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="P52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="R52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="S52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="T52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="U52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="V52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="W52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="X52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AS52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AV52" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AW52" s="23" t="s">
+      <c r="A52" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" t="s">
+        <v>4</v>
+      </c>
+      <c r="K52" t="s">
+        <v>4</v>
+      </c>
+      <c r="L52" t="s">
+        <v>4</v>
+      </c>
+      <c r="M52" t="s">
+        <v>4</v>
+      </c>
+      <c r="N52" t="s">
+        <v>4</v>
+      </c>
+      <c r="O52" t="s">
+        <v>4</v>
+      </c>
+      <c r="P52" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>4</v>
+      </c>
+      <c r="R52" t="s">
+        <v>4</v>
+      </c>
+      <c r="S52" t="s">
+        <v>4</v>
+      </c>
+      <c r="T52" t="s">
+        <v>4</v>
+      </c>
+      <c r="U52" t="s">
+        <v>4</v>
+      </c>
+      <c r="V52" t="s">
+        <v>4</v>
+      </c>
+      <c r="W52" t="s">
+        <v>4</v>
+      </c>
+      <c r="X52" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV52" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW52" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="E53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="H53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="K53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="L53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="M53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="N53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="O53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="P53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="R53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="S53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="T53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="U53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="V53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="W53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="X53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AS53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AV53" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AW53" s="23" t="s">
+      <c r="A53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" t="s">
+        <v>4</v>
+      </c>
+      <c r="E53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F53" t="s">
+        <v>4</v>
+      </c>
+      <c r="G53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H53" t="s">
+        <v>4</v>
+      </c>
+      <c r="I53" t="s">
+        <v>4</v>
+      </c>
+      <c r="J53" t="s">
+        <v>4</v>
+      </c>
+      <c r="K53" t="s">
+        <v>4</v>
+      </c>
+      <c r="L53" t="s">
+        <v>4</v>
+      </c>
+      <c r="M53" t="s">
+        <v>4</v>
+      </c>
+      <c r="N53" t="s">
+        <v>4</v>
+      </c>
+      <c r="O53" t="s">
+        <v>4</v>
+      </c>
+      <c r="P53" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>4</v>
+      </c>
+      <c r="R53" t="s">
+        <v>4</v>
+      </c>
+      <c r="S53" t="s">
+        <v>4</v>
+      </c>
+      <c r="T53" t="s">
+        <v>4</v>
+      </c>
+      <c r="U53" t="s">
+        <v>4</v>
+      </c>
+      <c r="V53" t="s">
+        <v>4</v>
+      </c>
+      <c r="W53" t="s">
+        <v>4</v>
+      </c>
+      <c r="X53" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV53" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW53" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="E54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="H54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="K54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="L54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="M54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="N54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="O54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="P54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="R54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="S54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="T54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="U54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="V54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="W54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="X54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AS54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AV54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AW54" s="23" t="s">
+      <c r="A54" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" t="s">
+        <v>4</v>
+      </c>
+      <c r="D54" t="s">
+        <v>4</v>
+      </c>
+      <c r="E54" t="s">
+        <v>4</v>
+      </c>
+      <c r="F54" t="s">
+        <v>4</v>
+      </c>
+      <c r="G54" t="s">
+        <v>4</v>
+      </c>
+      <c r="H54" t="s">
+        <v>4</v>
+      </c>
+      <c r="I54" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" t="s">
+        <v>4</v>
+      </c>
+      <c r="K54" t="s">
+        <v>4</v>
+      </c>
+      <c r="L54" t="s">
+        <v>4</v>
+      </c>
+      <c r="M54" t="s">
+        <v>4</v>
+      </c>
+      <c r="N54" t="s">
+        <v>4</v>
+      </c>
+      <c r="O54" t="s">
+        <v>4</v>
+      </c>
+      <c r="P54" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>4</v>
+      </c>
+      <c r="R54" t="s">
+        <v>4</v>
+      </c>
+      <c r="S54" t="s">
+        <v>4</v>
+      </c>
+      <c r="T54" t="s">
+        <v>4</v>
+      </c>
+      <c r="U54" t="s">
+        <v>4</v>
+      </c>
+      <c r="V54" t="s">
+        <v>4</v>
+      </c>
+      <c r="W54" t="s">
+        <v>4</v>
+      </c>
+      <c r="X54" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV54" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW54" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="E55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="H55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="K55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="L55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="M55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="N55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="O55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="P55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="R55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="S55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="T55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="U55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="V55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="W55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="X55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AS55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AV55" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AW55" s="23" t="s">
+      <c r="A55" t="s">
+        <v>4</v>
+      </c>
+      <c r="B55" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" t="s">
+        <v>4</v>
+      </c>
+      <c r="E55" t="s">
+        <v>4</v>
+      </c>
+      <c r="F55" t="s">
+        <v>4</v>
+      </c>
+      <c r="G55" t="s">
+        <v>4</v>
+      </c>
+      <c r="H55" t="s">
+        <v>4</v>
+      </c>
+      <c r="I55" t="s">
+        <v>4</v>
+      </c>
+      <c r="J55" t="s">
+        <v>4</v>
+      </c>
+      <c r="K55" t="s">
+        <v>4</v>
+      </c>
+      <c r="L55" t="s">
+        <v>4</v>
+      </c>
+      <c r="M55" t="s">
+        <v>4</v>
+      </c>
+      <c r="N55" t="s">
+        <v>4</v>
+      </c>
+      <c r="O55" t="s">
+        <v>4</v>
+      </c>
+      <c r="P55" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>4</v>
+      </c>
+      <c r="R55" t="s">
+        <v>4</v>
+      </c>
+      <c r="S55" t="s">
+        <v>4</v>
+      </c>
+      <c r="T55" t="s">
+        <v>4</v>
+      </c>
+      <c r="U55" t="s">
+        <v>4</v>
+      </c>
+      <c r="V55" t="s">
+        <v>4</v>
+      </c>
+      <c r="W55" t="s">
+        <v>4</v>
+      </c>
+      <c r="X55" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW55" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="E56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="H56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="K56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="L56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="M56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="N56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="O56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="P56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="R56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="S56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="T56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="U56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="V56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="W56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="X56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AS56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AU56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AV56" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="AW56" s="23" t="s">
+      <c r="A56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56" t="s">
+        <v>4</v>
+      </c>
+      <c r="E56" t="s">
+        <v>4</v>
+      </c>
+      <c r="F56" t="s">
+        <v>4</v>
+      </c>
+      <c r="G56" t="s">
+        <v>4</v>
+      </c>
+      <c r="H56" t="s">
+        <v>4</v>
+      </c>
+      <c r="I56" t="s">
+        <v>4</v>
+      </c>
+      <c r="J56" t="s">
+        <v>4</v>
+      </c>
+      <c r="K56" t="s">
+        <v>4</v>
+      </c>
+      <c r="L56" t="s">
+        <v>4</v>
+      </c>
+      <c r="M56" t="s">
+        <v>4</v>
+      </c>
+      <c r="N56" t="s">
+        <v>4</v>
+      </c>
+      <c r="O56" t="s">
+        <v>4</v>
+      </c>
+      <c r="P56" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>4</v>
+      </c>
+      <c r="R56" t="s">
+        <v>4</v>
+      </c>
+      <c r="S56" t="s">
+        <v>4</v>
+      </c>
+      <c r="T56" t="s">
+        <v>4</v>
+      </c>
+      <c r="U56" t="s">
+        <v>4</v>
+      </c>
+      <c r="V56" t="s">
+        <v>4</v>
+      </c>
+      <c r="W56" t="s">
+        <v>4</v>
+      </c>
+      <c r="X56" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW56" t="s">
         <v>4</v>
       </c>
     </row>
